--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N65_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>14.26197231271898</v>
       </c>
       <c r="E2" t="n">
-        <v>4.312355485306729</v>
+        <v>4.691275969235066</v>
       </c>
       <c r="F2" t="n">
-        <v>4.945424173820725</v>
+        <v>4.564422222282904</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>5.874337396390223</v>
       </c>
       <c r="E3" t="n">
-        <v>4.312355485306729</v>
+        <v>4.691275969235066</v>
       </c>
       <c r="F3" t="n">
-        <v>4.945424173820725</v>
+        <v>4.564422222282904</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>2.780433176258737</v>
       </c>
       <c r="E4" t="n">
-        <v>4.312355485306729</v>
+        <v>4.691275969235066</v>
       </c>
       <c r="F4" t="n">
-        <v>4.945424173820725</v>
+        <v>4.564422222282904</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.99386518970482</v>
+        <v>4.317483579830416</v>
       </c>
       <c r="D5" t="n">
-        <v>12.92470078729258</v>
+        <v>12.00613700394302</v>
       </c>
       <c r="E5" t="n">
-        <v>4.312355485306729</v>
+        <v>4.691275969235066</v>
       </c>
       <c r="F5" t="n">
-        <v>4.945424173820725</v>
+        <v>4.564422222282904</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,23 +608,55 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
+        <v>13.99386518970482</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12.92470078729258</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.691275969235066</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.564422222282904</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>T8387</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W0075F0003T0006Z000C1N65.png</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
         <v>15.7424244202163</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>15.15995558698251</v>
       </c>
-      <c r="E6" t="n">
-        <v>4.312355485306729</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.945424173820725</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="E7" t="n">
+        <v>4.691275969235066</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.564422222282904</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>T8387</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.21162986737009</v>
+        <v>2.30938985344764</v>
       </c>
       <c r="D2" t="n">
-        <v>14.26197231271898</v>
+        <v>2.317570500816835</v>
       </c>
       <c r="E2" t="n">
-        <v>4.691275969235066</v>
+        <v>0.7623323450006982</v>
       </c>
       <c r="F2" t="n">
-        <v>4.564422222282904</v>
+        <v>0.7417186111209718</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.737779113336976</v>
+        <v>0.9323891059172587</v>
       </c>
       <c r="D3" t="n">
-        <v>5.874337396390223</v>
+        <v>0.9545798269134111</v>
       </c>
       <c r="E3" t="n">
-        <v>4.691275969235066</v>
+        <v>0.7623323450006982</v>
       </c>
       <c r="F3" t="n">
-        <v>4.564422222282904</v>
+        <v>0.7417186111209718</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.13607580555443</v>
+        <v>0.997112318402595</v>
       </c>
       <c r="D4" t="n">
-        <v>2.780433176258737</v>
+        <v>0.4518203911420448</v>
       </c>
       <c r="E4" t="n">
-        <v>4.691275969235066</v>
+        <v>0.7623323450006982</v>
       </c>
       <c r="F4" t="n">
-        <v>4.564422222282904</v>
+        <v>0.7417186111209718</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.317483579830416</v>
+        <v>0.7015910817224426</v>
       </c>
       <c r="D5" t="n">
-        <v>12.00613700394302</v>
+        <v>1.950997263140741</v>
       </c>
       <c r="E5" t="n">
-        <v>4.691275969235066</v>
+        <v>0.7623323450006982</v>
       </c>
       <c r="F5" t="n">
-        <v>4.564422222282904</v>
+        <v>0.7417186111209718</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.99386518970482</v>
+        <v>2.274003093327034</v>
       </c>
       <c r="D6" t="n">
-        <v>12.92470078729258</v>
+        <v>2.100263877935045</v>
       </c>
       <c r="E6" t="n">
-        <v>4.691275969235066</v>
+        <v>0.7623323450006982</v>
       </c>
       <c r="F6" t="n">
-        <v>4.564422222282904</v>
+        <v>0.7417186111209718</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.7424244202163</v>
+        <v>2.55814396828515</v>
       </c>
       <c r="D7" t="n">
-        <v>15.15995558698251</v>
+        <v>2.463492782884657</v>
       </c>
       <c r="E7" t="n">
-        <v>4.691275969235066</v>
+        <v>0.7623323450006982</v>
       </c>
       <c r="F7" t="n">
-        <v>4.564422222282904</v>
+        <v>0.7417186111209718</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
